--- a/demo/base_etp_demo.xlsx
+++ b/demo/base_etp_demo.xlsx
@@ -5459,7 +5459,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S53"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5531,7 +5531,7 @@
         <v>Lambert Emma</v>
       </c>
       <c r="D2" t="str">
-        <v>Départ forcé</v>
+        <v>Transfert entrant</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -5540,7 +5540,7 @@
         <v>Achats</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>Production</v>
       </c>
       <c r="H2" t="str">
         <v>France</v>
@@ -5567,16 +5567,16 @@
         <v>Oui</v>
       </c>
       <c r="P2">
-        <v>-38000</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="R2">
         <v>2000</v>
       </c>
       <c r="S2" t="str">
-        <v>Mouvement de démo généré (départ forcé, lié à AC-001).</v>
+        <v>Mouvement de démo généré (transfert entrant, lié à AC-001, sans impact ETP net).</v>
       </c>
     </row>
     <row r="3">
@@ -5584,22 +5584,22 @@
         <v>MV-002</v>
       </c>
       <c r="B3" t="str">
-        <v>M006</v>
+        <v>M002</v>
       </c>
       <c r="C3" t="str">
-        <v>Klein Hans</v>
+        <v>Garnier Louis</v>
       </c>
       <c r="D3" t="str">
-        <v>Transfert entrant</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>Logistique</v>
+        <v>Production</v>
       </c>
       <c r="G3" t="str">
-        <v>Marketing</v>
+        <v/>
       </c>
       <c r="H3" t="str">
         <v>Germany</v>
@@ -5608,7 +5608,7 @@
         <v>Sophie Dubois</v>
       </c>
       <c r="J3" t="str">
-        <v>AC-004</v>
+        <v>AC-002</v>
       </c>
       <c r="K3" t="str">
         <v>2026-02-15</v>
@@ -5626,16 +5626,16 @@
         <v>Non</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>-38733</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>38733</v>
       </c>
       <c r="R3">
         <v>3500</v>
       </c>
       <c r="S3" t="str">
-        <v>Mouvement de démo généré (transfert entrant, lié à AC-004).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-002, -2 ETP).</v>
       </c>
     </row>
     <row r="4">
@@ -5643,13 +5643,13 @@
         <v>MV-003</v>
       </c>
       <c r="B4" t="str">
-        <v>M011</v>
+        <v>M003</v>
       </c>
       <c r="C4" t="str">
-        <v>Cole Ryan</v>
+        <v>Petit Camille</v>
       </c>
       <c r="D4" t="str">
-        <v>Transfert sortant</v>
+        <v>Attrition</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -5667,13 +5667,13 @@
         <v>Claire Moreau</v>
       </c>
       <c r="J4" t="str">
-        <v>AC-007</v>
+        <v>AC-002</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-03-15</v>
+        <v>2026-04-15</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-03-15</v>
+        <v>2026-04-15</v>
       </c>
       <c r="M4" t="str">
         <v>Réalisé</v>
@@ -5685,16 +5685,16 @@
         <v>Non</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>-39466</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>39466</v>
       </c>
       <c r="R4">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="S4" t="str">
-        <v>Mouvement de démo généré (transfert sortant, lié à AC-007).</v>
+        <v>Mouvement de démo généré (attrition, lié à AC-002, -1 ETP).</v>
       </c>
     </row>
     <row r="5">
@@ -5702,16 +5702,16 @@
         <v>MV-004</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>M004</v>
       </c>
       <c r="C5" t="str">
-        <v>Poste à recruter (AC-010)</v>
+        <v>Roy Antoine</v>
       </c>
       <c r="D5" t="str">
-        <v>Recrutement</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="str">
         <v>Finance</v>
@@ -5726,34 +5726,34 @@
         <v>Claire Moreau</v>
       </c>
       <c r="J5" t="str">
-        <v>AC-010</v>
+        <v>AC-003</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-04-15</v>
+        <v>2026-03-15</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>2026-03-15</v>
       </c>
       <c r="M5" t="str">
-        <v>Planifié</v>
+        <v>Réalisé</v>
       </c>
       <c r="N5" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="O5" t="str">
         <v>Non</v>
       </c>
       <c r="P5">
-        <v>45000</v>
+        <v>-40199</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>40199</v>
       </c>
       <c r="R5">
-        <v>6500</v>
+        <v>5000</v>
       </c>
       <c r="S5" t="str">
-        <v>Mouvement de démo généré (recrutement, lié à AC-010).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-003, -2 ETP).</v>
       </c>
     </row>
     <row r="6">
@@ -5761,13 +5761,13 @@
         <v>MV-005</v>
       </c>
       <c r="B6" t="str">
-        <v>M021</v>
+        <v>M005</v>
       </c>
       <c r="C6" t="str">
-        <v>Garnier Emma</v>
+        <v>Moreau Julie</v>
       </c>
       <c r="D6" t="str">
-        <v>Départ forcé</v>
+        <v>Attrition</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -5785,7 +5785,7 @@
         <v>Sophie Dubois</v>
       </c>
       <c r="J6" t="str">
-        <v>AC-013</v>
+        <v>AC-003</v>
       </c>
       <c r="K6" t="str">
         <v>2026-05-15</v>
@@ -5794,7 +5794,7 @@
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>À faire</v>
+        <v>Planifié</v>
       </c>
       <c r="N6" t="str">
         <v>Non</v>
@@ -5803,16 +5803,16 @@
         <v>Non</v>
       </c>
       <c r="P6">
-        <v>-52660</v>
+        <v>-40932</v>
       </c>
       <c r="Q6">
-        <v>52660</v>
+        <v>40932</v>
       </c>
       <c r="R6">
         <v>8000</v>
       </c>
       <c r="S6" t="str">
-        <v>Mouvement de démo généré (départ forcé, lié à AC-013).</v>
+        <v>Mouvement de démo généré (attrition, lié à AC-003, -1 ETP).</v>
       </c>
     </row>
     <row r="7">
@@ -5820,22 +5820,22 @@
         <v>MV-006</v>
       </c>
       <c r="B7" t="str">
-        <v>M026</v>
+        <v>M006</v>
       </c>
       <c r="C7" t="str">
-        <v>Fontaine Hans</v>
+        <v>Klein Hans</v>
       </c>
       <c r="D7" t="str">
-        <v>Transfert entrant</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>Production</v>
+        <v>Logistique</v>
       </c>
       <c r="G7" t="str">
-        <v>IT</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v>Germany</v>
@@ -5844,34 +5844,34 @@
         <v>Sophie Dubois</v>
       </c>
       <c r="J7" t="str">
-        <v>AC-016</v>
+        <v>AC-003</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-06-15</v>
+        <v>2026-07-15</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="M7" t="str">
-        <v>Réalisé</v>
+        <v>À faire</v>
       </c>
       <c r="N7" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="O7" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>-41665</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>41665</v>
       </c>
       <c r="R7">
-        <v>9500</v>
+        <v>2000</v>
       </c>
       <c r="S7" t="str">
-        <v>Mouvement de démo généré (transfert entrant, lié à AC-016).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-003, -1 ETP).</v>
       </c>
     </row>
     <row r="8">
@@ -5879,16 +5879,16 @@
         <v>MV-007</v>
       </c>
       <c r="B8" t="str">
-        <v>M031</v>
+        <v>M007</v>
       </c>
       <c r="C8" t="str">
-        <v>Bennett Ryan</v>
+        <v>Fontaine Léa</v>
       </c>
       <c r="D8" t="str">
-        <v>Transfert sortant</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F8" t="str">
         <v>IT</v>
@@ -5903,10 +5903,10 @@
         <v>Claire Moreau</v>
       </c>
       <c r="J8" t="str">
-        <v>AC-019</v>
+        <v>AC-004</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-07-15</v>
+        <v>2026-04-15</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -5921,16 +5921,16 @@
         <v>Non</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>-42398</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>42398</v>
       </c>
       <c r="R8">
-        <v>2000</v>
+        <v>6500</v>
       </c>
       <c r="S8" t="str">
-        <v>Mouvement de démo généré (transfert sortant, lié à AC-019).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-004, -5 ETP).</v>
       </c>
     </row>
     <row r="9">
@@ -5938,13 +5938,13 @@
         <v>MV-008</v>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>M008</v>
       </c>
       <c r="C9" t="str">
-        <v>Poste à recruter (AC-022)</v>
+        <v>Weber Paul</v>
       </c>
       <c r="D9" t="str">
-        <v>Recrutement</v>
+        <v>Transfert entrant</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5953,7 +5953,7 @@
         <v>RH</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>Logistique</v>
       </c>
       <c r="H9" t="str">
         <v>USA</v>
@@ -5962,10 +5962,10 @@
         <v>Claire Moreau</v>
       </c>
       <c r="J9" t="str">
-        <v>AC-022</v>
+        <v>AC-005</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-08-15</v>
+        <v>2026-05-15</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -5980,16 +5980,16 @@
         <v>Non</v>
       </c>
       <c r="P9">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>3500</v>
+        <v>8000</v>
       </c>
       <c r="S9" t="str">
-        <v>Mouvement de démo généré (recrutement, lié à AC-022).</v>
+        <v>Mouvement de démo généré (transfert entrant, lié à AC-005, sans impact ETP net).</v>
       </c>
     </row>
     <row r="10">
@@ -5997,10 +5997,10 @@
         <v>MV-009</v>
       </c>
       <c r="B10" t="str">
-        <v>M041</v>
+        <v>M009</v>
       </c>
       <c r="C10" t="str">
-        <v>Petit Emma</v>
+        <v>Ruiz Sofia</v>
       </c>
       <c r="D10" t="str">
         <v>Départ forcé</v>
@@ -6021,13 +6021,13 @@
         <v>Sophie Dubois</v>
       </c>
       <c r="J10" t="str">
-        <v>AC-025</v>
+        <v>AC-006</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-09-15</v>
+        <v>2026-06-15</v>
       </c>
       <c r="L10" t="str">
-        <v>2026-09-15</v>
+        <v>2026-06-15</v>
       </c>
       <c r="M10" t="str">
         <v>Réalisé</v>
@@ -6036,19 +6036,19 @@
         <v>Oui</v>
       </c>
       <c r="O10" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="P10">
-        <v>-67320</v>
+        <v>-43864</v>
       </c>
       <c r="Q10">
-        <v>67320</v>
+        <v>43864</v>
       </c>
       <c r="R10">
-        <v>5000</v>
+        <v>9500</v>
       </c>
       <c r="S10" t="str">
-        <v>Mouvement de démo généré (départ forcé, lié à AC-025).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-006, -1 ETP).</v>
       </c>
     </row>
     <row r="11">
@@ -6056,22 +6056,22 @@
         <v>MV-010</v>
       </c>
       <c r="B11" t="str">
-        <v>M046</v>
+        <v>M010</v>
       </c>
       <c r="C11" t="str">
-        <v>Weber Hans</v>
+        <v>Diaz Mateo</v>
       </c>
       <c r="D11" t="str">
-        <v>Transfert entrant</v>
+        <v>Attrition</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>Logistique</v>
+        <v>Production</v>
       </c>
       <c r="G11" t="str">
-        <v>Marketing</v>
+        <v/>
       </c>
       <c r="H11" t="str">
         <v>Germany</v>
@@ -6080,10 +6080,10 @@
         <v>Sophie Dubois</v>
       </c>
       <c r="J11" t="str">
-        <v>AC-028</v>
+        <v>AC-006</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-10-15</v>
+        <v>2026-08-15</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -6098,16 +6098,16 @@
         <v>Non</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>-44597</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>44597</v>
       </c>
       <c r="R11">
-        <v>6500</v>
+        <v>3500</v>
       </c>
       <c r="S11" t="str">
-        <v>Mouvement de démo généré (transfert entrant, lié à AC-028).</v>
+        <v>Mouvement de démo généré (attrition, lié à AC-006, -1 ETP).</v>
       </c>
     </row>
     <row r="12">
@@ -6115,16 +6115,16 @@
         <v>MV-011</v>
       </c>
       <c r="B12" t="str">
-        <v>M051</v>
+        <v>M011</v>
       </c>
       <c r="C12" t="str">
-        <v>Girard Ryan</v>
+        <v>Cole Ryan</v>
       </c>
       <c r="D12" t="str">
-        <v>Transfert sortant</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="str">
         <v>Marketing</v>
@@ -6139,34 +6139,34 @@
         <v>Claire Moreau</v>
       </c>
       <c r="J12" t="str">
-        <v>AC-001</v>
+        <v>AC-007</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-11-15</v>
+        <v>2026-07-15</v>
       </c>
       <c r="L12" t="str">
         <v/>
       </c>
       <c r="M12" t="str">
-        <v>À faire</v>
+        <v>Planifié</v>
       </c>
       <c r="N12" t="str">
         <v>Non</v>
       </c>
       <c r="O12" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>-45330</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>45330</v>
       </c>
       <c r="R12">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="S12" t="str">
-        <v>Mouvement de démo généré (transfert sortant, lié à AC-001).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-007, -3 ETP).</v>
       </c>
     </row>
     <row r="13">
@@ -6174,16 +6174,16 @@
         <v>MV-012</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>M012</v>
       </c>
       <c r="C13" t="str">
-        <v>Poste à recruter (AC-004)</v>
+        <v>Bennett Sarah</v>
       </c>
       <c r="D13" t="str">
-        <v>Recrutement</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="str">
         <v>Finance</v>
@@ -6198,34 +6198,34 @@
         <v>Claire Moreau</v>
       </c>
       <c r="J13" t="str">
-        <v>AC-004</v>
+        <v>AC-008</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-12-15</v>
+        <v>2026-08-15</v>
       </c>
       <c r="L13" t="str">
-        <v>2026-12-15</v>
+        <v/>
       </c>
       <c r="M13" t="str">
-        <v>Réalisé</v>
+        <v>À faire</v>
       </c>
       <c r="N13" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="O13" t="str">
         <v>Non</v>
       </c>
       <c r="P13">
-        <v>45000</v>
+        <v>-46063</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>46063</v>
       </c>
       <c r="R13">
-        <v>9500</v>
+        <v>3500</v>
       </c>
       <c r="S13" t="str">
-        <v>Mouvement de démo généré (recrutement, lié à AC-004).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-008, -2 ETP).</v>
       </c>
     </row>
     <row r="14">
@@ -6233,16 +6233,16 @@
         <v>MV-013</v>
       </c>
       <c r="B14" t="str">
-        <v>M061</v>
+        <v>M013</v>
       </c>
       <c r="C14" t="str">
-        <v>Roy Emma</v>
+        <v>Girard Nadia</v>
       </c>
       <c r="D14" t="str">
-        <v>Départ forcé</v>
+        <v>Attrition</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="str">
         <v>Ventes</v>
@@ -6257,34 +6257,34 @@
         <v>Sophie Dubois</v>
       </c>
       <c r="J14" t="str">
-        <v>AC-007</v>
+        <v>AC-008</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-01-15</v>
+        <v>2026-10-15</v>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>2026-10-15</v>
       </c>
       <c r="M14" t="str">
-        <v>Planifié</v>
+        <v>Réalisé</v>
       </c>
       <c r="N14" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="O14" t="str">
         <v>Non</v>
       </c>
       <c r="P14">
-        <v>-39980</v>
+        <v>-46796</v>
       </c>
       <c r="Q14">
-        <v>39980</v>
+        <v>46796</v>
       </c>
       <c r="R14">
-        <v>2000</v>
+        <v>6500</v>
       </c>
       <c r="S14" t="str">
-        <v>Mouvement de démo généré (départ forcé, lié à AC-007).</v>
+        <v>Mouvement de démo généré (attrition, lié à AC-008, -2 ETP).</v>
       </c>
     </row>
     <row r="15">
@@ -6292,10 +6292,10 @@
         <v>MV-014</v>
       </c>
       <c r="B15" t="str">
-        <v>M066</v>
+        <v>M014</v>
       </c>
       <c r="C15" t="str">
-        <v>Ruiz Hans</v>
+        <v>Bernard Marc</v>
       </c>
       <c r="D15" t="str">
         <v>Transfert entrant</v>
@@ -6304,10 +6304,10 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="G15" t="str">
         <v>Production</v>
-      </c>
-      <c r="G15" t="str">
-        <v>IT</v>
       </c>
       <c r="H15" t="str">
         <v>Germany</v>
@@ -6316,19 +6316,19 @@
         <v>Sophie Dubois</v>
       </c>
       <c r="J15" t="str">
-        <v>AC-010</v>
+        <v>AC-009</v>
       </c>
       <c r="K15" t="str">
-        <v>2026-02-15</v>
+        <v>2026-09-15</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>2026-09-15</v>
       </c>
       <c r="M15" t="str">
-        <v>À faire</v>
+        <v>Réalisé</v>
       </c>
       <c r="N15" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="O15" t="str">
         <v>Non</v>
@@ -6340,10 +6340,10 @@
         <v>0</v>
       </c>
       <c r="R15">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="S15" t="str">
-        <v>Mouvement de démo généré (transfert entrant, lié à AC-010).</v>
+        <v>Mouvement de démo généré (transfert entrant, lié à AC-009, sans impact ETP net).</v>
       </c>
     </row>
     <row r="16">
@@ -6351,16 +6351,16 @@
         <v>MV-015</v>
       </c>
       <c r="B16" t="str">
-        <v>M071</v>
+        <v>M015</v>
       </c>
       <c r="C16" t="str">
-        <v>Bernard Ryan</v>
+        <v>Alvarez Elena</v>
       </c>
       <c r="D16" t="str">
-        <v>Transfert sortant</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F16" t="str">
         <v>IT</v>
@@ -6375,34 +6375,34 @@
         <v>Claire Moreau</v>
       </c>
       <c r="J16" t="str">
-        <v>AC-013</v>
+        <v>AC-010</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-03-15</v>
+        <v>2026-10-15</v>
       </c>
       <c r="L16" t="str">
-        <v>2026-03-15</v>
+        <v/>
       </c>
       <c r="M16" t="str">
-        <v>Réalisé</v>
+        <v>Planifié</v>
       </c>
       <c r="N16" t="str">
-        <v>Oui</v>
+        <v>Non</v>
       </c>
       <c r="O16" t="str">
         <v>Non</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>-48262</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>48262</v>
       </c>
       <c r="R16">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="S16" t="str">
-        <v>Mouvement de démo généré (transfert sortant, lié à AC-013).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-010, -6 ETP).</v>
       </c>
     </row>
     <row r="17">
@@ -6410,13 +6410,13 @@
         <v>MV-016</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>M016</v>
       </c>
       <c r="C17" t="str">
-        <v>Poste à recruter (AC-016)</v>
+        <v>Dahl Thomas</v>
       </c>
       <c r="D17" t="str">
-        <v>Recrutement</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -6434,16 +6434,16 @@
         <v>Claire Moreau</v>
       </c>
       <c r="J17" t="str">
-        <v>AC-016</v>
+        <v>AC-011</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-04-15</v>
+        <v>2026-11-15</v>
       </c>
       <c r="L17" t="str">
         <v/>
       </c>
       <c r="M17" t="str">
-        <v>Planifié</v>
+        <v>À faire</v>
       </c>
       <c r="N17" t="str">
         <v>Non</v>
@@ -6452,16 +6452,16 @@
         <v>Oui</v>
       </c>
       <c r="P17">
-        <v>45000</v>
+        <v>-48995</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>48995</v>
       </c>
       <c r="R17">
-        <v>6500</v>
+        <v>8000</v>
       </c>
       <c r="S17" t="str">
-        <v>Mouvement de démo généré (recrutement, lié à AC-016).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-011, -1 ETP).</v>
       </c>
     </row>
     <row r="18">
@@ -6469,13 +6469,13 @@
         <v>MV-017</v>
       </c>
       <c r="B18" t="str">
-        <v>M081</v>
+        <v>M017</v>
       </c>
       <c r="C18" t="str">
-        <v>Moreau Emma</v>
+        <v>Vasseur Claire</v>
       </c>
       <c r="D18" t="str">
-        <v>Départ forcé</v>
+        <v>Attrition</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -6493,34 +6493,34 @@
         <v>Sophie Dubois</v>
       </c>
       <c r="J18" t="str">
-        <v>AC-019</v>
+        <v>AC-011</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-05-15</v>
+        <v>2026-01-15</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>2026-01-15</v>
       </c>
       <c r="M18" t="str">
-        <v>À faire</v>
+        <v>Réalisé</v>
       </c>
       <c r="N18" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="O18" t="str">
         <v>Non</v>
       </c>
       <c r="P18">
-        <v>-54640</v>
+        <v>-49728</v>
       </c>
       <c r="Q18">
-        <v>54640</v>
+        <v>49728</v>
       </c>
       <c r="R18">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="S18" t="str">
-        <v>Mouvement de démo généré (départ forcé, lié à AC-019).</v>
+        <v>Mouvement de démo généré (attrition, lié à AC-011, -1 ETP).</v>
       </c>
     </row>
     <row r="19">
@@ -6528,22 +6528,22 @@
         <v>MV-018</v>
       </c>
       <c r="B19" t="str">
-        <v>M086</v>
+        <v>M018</v>
       </c>
       <c r="C19" t="str">
-        <v>Diaz Hans</v>
+        <v>Blanc Julien</v>
       </c>
       <c r="D19" t="str">
-        <v>Transfert entrant</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>Logistique</v>
+        <v>Production</v>
       </c>
       <c r="G19" t="str">
-        <v>Marketing</v>
+        <v/>
       </c>
       <c r="H19" t="str">
         <v>Germany</v>
@@ -6552,13 +6552,13 @@
         <v>Sophie Dubois</v>
       </c>
       <c r="J19" t="str">
-        <v>AC-022</v>
+        <v>AC-012</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-06-15</v>
+        <v>2026-12-15</v>
       </c>
       <c r="L19" t="str">
-        <v>2026-06-15</v>
+        <v>2026-12-15</v>
       </c>
       <c r="M19" t="str">
         <v>Réalisé</v>
@@ -6570,16 +6570,16 @@
         <v>Non</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>-50461</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>50461</v>
       </c>
       <c r="R19">
         <v>9500</v>
       </c>
       <c r="S19" t="str">
-        <v>Mouvement de démo généré (transfert entrant, lié à AC-022).</v>
+        <v>Mouvement de démo généré (départ forcé, lié à AC-012, -1 ETP).</v>
       </c>
     </row>
     <row r="20">
@@ -6587,13 +6587,13 @@
         <v>MV-019</v>
       </c>
       <c r="B20" t="str">
-        <v>M091</v>
+        <v>M019</v>
       </c>
       <c r="C20" t="str">
-        <v>Alvarez Ryan</v>
+        <v>Nystrom Henrik</v>
       </c>
       <c r="D20" t="str">
-        <v>Transfert sortant</v>
+        <v>Attrition</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -6611,10 +6611,10 @@
         <v>Claire Moreau</v>
       </c>
       <c r="J20" t="str">
-        <v>AC-025</v>
+        <v>AC-012</v>
       </c>
       <c r="K20" t="str">
-        <v>2026-07-15</v>
+        <v>2026-02-15</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -6629,16 +6629,16 @@
         <v>Non</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>-51194</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>51194</v>
       </c>
       <c r="R20">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="S20" t="str">
-        <v>Mouvement de démo généré (transfert sortant, lié à AC-025).</v>
+        <v>Mouvement de démo généré (attrition, lié à AC-012, -1 ETP).</v>
       </c>
     </row>
     <row r="21">
@@ -6646,13 +6646,13 @@
         <v>MV-020</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>M020</v>
       </c>
       <c r="C21" t="str">
-        <v>Poste à recruter (AC-028)</v>
+        <v>Keller Ines</v>
       </c>
       <c r="D21" t="str">
-        <v>Recrutement</v>
+        <v>Départ forcé</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -6670,10 +6670,10 @@
         <v>Claire Moreau</v>
       </c>
       <c r="J21" t="str">
-        <v>AC-028</v>
+        <v>AC-012</v>
       </c>
       <c r="K21" t="str">
-        <v>2026-08-15</v>
+        <v>2026-04-15</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -6685,24 +6685,1912 @@
         <v>Non</v>
       </c>
       <c r="O21" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="P21">
+        <v>-51927</v>
+      </c>
+      <c r="Q21">
+        <v>51927</v>
+      </c>
+      <c r="R21">
+        <v>6500</v>
+      </c>
+      <c r="S21" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-012, -1 ETP).</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>MV-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>M021</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Garnier Emma</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Transfert entrant</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="H22" t="str">
+        <v>France</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J22" t="str">
+        <v>AC-013</v>
+      </c>
+      <c r="K22" t="str">
+        <v>2026-01-15</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N22" t="str">
         <v>Non</v>
       </c>
-      <c r="P21">
-        <v>45000</v>
-      </c>
-      <c r="Q21">
+      <c r="O22" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P22">
         <v>0</v>
       </c>
-      <c r="R21">
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>2000</v>
+      </c>
+      <c r="S22" t="str">
+        <v>Mouvement de démo généré (transfert entrant, lié à AC-013, sans impact ETP net).</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>MV-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>M022</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Petit Louis</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J23" t="str">
+        <v>AC-014</v>
+      </c>
+      <c r="K23" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="N23" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O23" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P23">
+        <v>-53393</v>
+      </c>
+      <c r="Q23">
+        <v>53393</v>
+      </c>
+      <c r="R23">
         <v>3500</v>
       </c>
-      <c r="S21" t="str">
-        <v>Mouvement de démo généré (recrutement, lié à AC-028).</v>
+      <c r="S23" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-014, -3 ETP).</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>MV-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>M023</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Roy Camille</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Attrition</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24" t="str">
+        <v>IT</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J24" t="str">
+        <v>AC-014</v>
+      </c>
+      <c r="K24" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="L24" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N24" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O24" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="P24">
+        <v>-54126</v>
+      </c>
+      <c r="Q24">
+        <v>54126</v>
+      </c>
+      <c r="R24">
+        <v>6500</v>
+      </c>
+      <c r="S24" t="str">
+        <v>Mouvement de démo généré (attrition, lié à AC-014, -2 ETP).</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>MV-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>M024</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Moreau Antoine</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25" t="str">
+        <v>RH</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>USA</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J25" t="str">
+        <v>AC-015</v>
+      </c>
+      <c r="K25" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="L25" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N25" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O25" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P25">
+        <v>-54859</v>
+      </c>
+      <c r="Q25">
+        <v>54859</v>
+      </c>
+      <c r="R25">
+        <v>5000</v>
+      </c>
+      <c r="S25" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-015, -2 ETP).</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>MV-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>M025</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Klein Julie</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Attrition</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>France</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J26" t="str">
+        <v>AC-015</v>
+      </c>
+      <c r="K26" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N26" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O26" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P26">
+        <v>-55592</v>
+      </c>
+      <c r="Q26">
+        <v>55592</v>
+      </c>
+      <c r="R26">
+        <v>8000</v>
+      </c>
+      <c r="S26" t="str">
+        <v>Mouvement de démo généré (attrition, lié à AC-015, -2 ETP).</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>MV-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>M026</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Fontaine Hans</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Production</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J27" t="str">
+        <v>AC-015</v>
+      </c>
+      <c r="K27" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="N27" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O27" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P27">
+        <v>-56325</v>
+      </c>
+      <c r="Q27">
+        <v>56325</v>
+      </c>
+      <c r="R27">
+        <v>2000</v>
+      </c>
+      <c r="S27" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-015, -2 ETP).</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>MV-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>M027</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Weber Léa</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J28" t="str">
+        <v>AC-016</v>
+      </c>
+      <c r="K28" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N28" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O28" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="P28">
+        <v>-57058</v>
+      </c>
+      <c r="Q28">
+        <v>57058</v>
+      </c>
+      <c r="R28">
+        <v>6500</v>
+      </c>
+      <c r="S28" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-016, -2 ETP).</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>MV-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>M028</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Ruiz Paul</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Transfert entrant</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Production</v>
+      </c>
+      <c r="H29" t="str">
+        <v>USA</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J29" t="str">
+        <v>AC-017</v>
+      </c>
+      <c r="K29" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="N29" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O29" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>8000</v>
+      </c>
+      <c r="S29" t="str">
+        <v>Mouvement de démo généré (transfert entrant, lié à AC-017, sans impact ETP net).</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>MV-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>M029</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Diaz Sofia</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>France</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J30" t="str">
+        <v>AC-018</v>
+      </c>
+      <c r="K30" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="L30" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N30" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O30" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P30">
+        <v>-58524</v>
+      </c>
+      <c r="Q30">
+        <v>58524</v>
+      </c>
+      <c r="R30">
+        <v>9500</v>
+      </c>
+      <c r="S30" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-018, -2 ETP).</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>MV-030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>M030</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Cole Mateo</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Attrition</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J31" t="str">
+        <v>AC-018</v>
+      </c>
+      <c r="K31" t="str">
+        <v>2026-08-15</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N31" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O31" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P31">
+        <v>-59257</v>
+      </c>
+      <c r="Q31">
+        <v>59257</v>
+      </c>
+      <c r="R31">
+        <v>3500</v>
+      </c>
+      <c r="S31" t="str">
+        <v>Mouvement de démo généré (attrition, lié à AC-018, -1 ETP).</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>MV-031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>M031</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Bennett Ryan</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="str">
+        <v>IT</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J32" t="str">
+        <v>AC-018</v>
+      </c>
+      <c r="K32" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="N32" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O32" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P32">
+        <v>-59990</v>
+      </c>
+      <c r="Q32">
+        <v>59990</v>
+      </c>
+      <c r="R32">
+        <v>6500</v>
+      </c>
+      <c r="S32" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-018, -1 ETP).</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>MV-032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>M032</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Girard Sarah</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E33">
+        <v>5</v>
+      </c>
+      <c r="F33" t="str">
+        <v>RH</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>USA</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J33" t="str">
+        <v>AC-019</v>
+      </c>
+      <c r="K33" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N33" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O33" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P33">
+        <v>-60723</v>
+      </c>
+      <c r="Q33">
+        <v>60723</v>
+      </c>
+      <c r="R33">
+        <v>2000</v>
+      </c>
+      <c r="S33" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-019, -5 ETP).</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>MV-033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>M033</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Bernard Nadia</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E34">
+        <v>3</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v>France</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J34" t="str">
+        <v>AC-020</v>
+      </c>
+      <c r="K34" t="str">
+        <v>2026-08-15</v>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="N34" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O34" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P34">
+        <v>-61456</v>
+      </c>
+      <c r="Q34">
+        <v>61456</v>
+      </c>
+      <c r="R34">
+        <v>3500</v>
+      </c>
+      <c r="S34" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-020, -3 ETP).</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>MV-034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>M034</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Alvarez Marc</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Attrition</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Production</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J35" t="str">
+        <v>AC-020</v>
+      </c>
+      <c r="K35" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="L35" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N35" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O35" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P35">
+        <v>-62189</v>
+      </c>
+      <c r="Q35">
+        <v>62189</v>
+      </c>
+      <c r="R35">
+        <v>6500</v>
+      </c>
+      <c r="S35" t="str">
+        <v>Mouvement de démo généré (attrition, lié à AC-020, -3 ETP).</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>MV-035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>M035</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Dahl Elena</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Transfert entrant</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J36" t="str">
+        <v>AC-021</v>
+      </c>
+      <c r="K36" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="L36" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="M36" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N36" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O36" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>5000</v>
+      </c>
+      <c r="S36" t="str">
+        <v>Mouvement de démo généré (transfert entrant, lié à AC-021, sans impact ETP net).</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>MV-036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>M036</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Vasseur Thomas</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E37">
+        <v>3</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>USA</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J37" t="str">
+        <v>AC-022</v>
+      </c>
+      <c r="K37" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N37" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O37" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P37">
+        <v>-63655</v>
+      </c>
+      <c r="Q37">
+        <v>63655</v>
+      </c>
+      <c r="R37">
+        <v>6500</v>
+      </c>
+      <c r="S37" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-022, -3 ETP).</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>MV-037</v>
+      </c>
+      <c r="B38" t="str">
+        <v>M037</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Blanc Claire</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>France</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J38" t="str">
+        <v>AC-023</v>
+      </c>
+      <c r="K38" t="str">
+        <v>2026-11-15</v>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="N38" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O38" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P38">
+        <v>-64388</v>
+      </c>
+      <c r="Q38">
+        <v>64388</v>
+      </c>
+      <c r="R38">
+        <v>8000</v>
+      </c>
+      <c r="S38" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-023, -2 ETP).</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>MV-038</v>
+      </c>
+      <c r="B39" t="str">
+        <v>M038</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Nystrom Julien</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Attrition</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J39" t="str">
+        <v>AC-023</v>
+      </c>
+      <c r="K39" t="str">
+        <v>2026-01-15</v>
+      </c>
+      <c r="L39" t="str">
+        <v>2026-01-15</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N39" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O39" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P39">
+        <v>-65121</v>
+      </c>
+      <c r="Q39">
+        <v>65121</v>
+      </c>
+      <c r="R39">
+        <v>2000</v>
+      </c>
+      <c r="S39" t="str">
+        <v>Mouvement de démo généré (attrition, lié à AC-023, -2 ETP).</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>MV-039</v>
+      </c>
+      <c r="B40" t="str">
+        <v>M039</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Keller Henrik</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40" t="str">
+        <v>IT</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J40" t="str">
+        <v>AC-024</v>
+      </c>
+      <c r="K40" t="str">
+        <v>2026-12-15</v>
+      </c>
+      <c r="L40" t="str">
+        <v>2026-12-15</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N40" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O40" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P40">
+        <v>-65854</v>
+      </c>
+      <c r="Q40">
+        <v>65854</v>
+      </c>
+      <c r="R40">
+        <v>9500</v>
+      </c>
+      <c r="S40" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-024, -2 ETP).</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>MV-040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>M040</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Lambert Ines</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Attrition</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="F41" t="str">
+        <v>RH</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v>USA</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J41" t="str">
+        <v>AC-024</v>
+      </c>
+      <c r="K41" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N41" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O41" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="P41">
+        <v>-66587</v>
+      </c>
+      <c r="Q41">
+        <v>66587</v>
+      </c>
+      <c r="R41">
+        <v>3500</v>
+      </c>
+      <c r="S41" t="str">
+        <v>Mouvement de démo généré (attrition, lié à AC-024, -2 ETP).</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>MV-041</v>
+      </c>
+      <c r="B42" t="str">
+        <v>M041</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Petit Emma</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v>France</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J42" t="str">
+        <v>AC-024</v>
+      </c>
+      <c r="K42" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="N42" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O42" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P42">
+        <v>-67320</v>
+      </c>
+      <c r="Q42">
+        <v>67320</v>
+      </c>
+      <c r="R42">
+        <v>6500</v>
+      </c>
+      <c r="S42" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-024, -1 ETP).</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>MV-042</v>
+      </c>
+      <c r="B43" t="str">
+        <v>M042</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Roy Louis</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Transfert entrant</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Production</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Production</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J43" t="str">
+        <v>AC-025</v>
+      </c>
+      <c r="K43" t="str">
+        <v>2026-01-15</v>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N43" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O43" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>2000</v>
+      </c>
+      <c r="S43" t="str">
+        <v>Mouvement de démo généré (transfert entrant, lié à AC-025, sans impact ETP net).</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>MV-043</v>
+      </c>
+      <c r="B44" t="str">
+        <v>M043</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Moreau Camille</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J44" t="str">
+        <v>AC-026</v>
+      </c>
+      <c r="K44" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="N44" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O44" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="P44">
+        <v>-68786</v>
+      </c>
+      <c r="Q44">
+        <v>68786</v>
+      </c>
+      <c r="R44">
+        <v>3500</v>
+      </c>
+      <c r="S44" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-026, -1 ETP).</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>MV-044</v>
+      </c>
+      <c r="B45" t="str">
+        <v>M044</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Klein Antoine</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Attrition</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v>USA</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J45" t="str">
+        <v>AC-026</v>
+      </c>
+      <c r="K45" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="L45" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N45" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O45" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P45">
+        <v>-69519</v>
+      </c>
+      <c r="Q45">
+        <v>69519</v>
+      </c>
+      <c r="R45">
+        <v>6500</v>
+      </c>
+      <c r="S45" t="str">
+        <v>Mouvement de démo généré (attrition, lié à AC-026, -1 ETP).</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>MV-045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>M045</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Fontaine Julie</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Ventes</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>France</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J46" t="str">
+        <v>AC-027</v>
+      </c>
+      <c r="K46" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="L46" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="M46" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N46" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O46" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P46">
+        <v>-70252</v>
+      </c>
+      <c r="Q46">
+        <v>70252</v>
+      </c>
+      <c r="R46">
+        <v>5000</v>
+      </c>
+      <c r="S46" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-027, -1 ETP).</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>MV-046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>M046</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Weber Hans</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Attrition</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J47" t="str">
+        <v>AC-027</v>
+      </c>
+      <c r="K47" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N47" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O47" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P47">
+        <v>-70985</v>
+      </c>
+      <c r="Q47">
+        <v>70985</v>
+      </c>
+      <c r="R47">
+        <v>8000</v>
+      </c>
+      <c r="S47" t="str">
+        <v>Mouvement de démo généré (attrition, lié à AC-027, -1 ETP).</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>MV-047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>M047</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Ruiz Léa</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48" t="str">
+        <v>IT</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J48" t="str">
+        <v>AC-027</v>
+      </c>
+      <c r="K48" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="N48" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O48" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="P48">
+        <v>-71718</v>
+      </c>
+      <c r="Q48">
+        <v>71718</v>
+      </c>
+      <c r="R48">
+        <v>2000</v>
+      </c>
+      <c r="S48" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-027, -1 ETP).</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>MV-048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>M048</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Diaz Paul</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E49">
+        <v>4</v>
+      </c>
+      <c r="F49" t="str">
+        <v>RH</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v>USA</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J49" t="str">
+        <v>AC-028</v>
+      </c>
+      <c r="K49" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N49" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O49" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P49">
+        <v>-72451</v>
+      </c>
+      <c r="Q49">
+        <v>72451</v>
+      </c>
+      <c r="R49">
+        <v>6500</v>
+      </c>
+      <c r="S49" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-028, -4 ETP).</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>MV-049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>M049</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Cole Sofia</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Transfert entrant</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Logistique</v>
+      </c>
+      <c r="H50" t="str">
+        <v>France</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J50" t="str">
+        <v>AC-029</v>
+      </c>
+      <c r="K50" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="N50" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O50" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>8000</v>
+      </c>
+      <c r="S50" t="str">
+        <v>Mouvement de démo généré (transfert entrant, lié à AC-029, sans impact ETP net).</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>MV-050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>M050</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Bennett Mateo</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Production</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Sophie Dubois</v>
+      </c>
+      <c r="J51" t="str">
+        <v>AC-030</v>
+      </c>
+      <c r="K51" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="L51" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="M51" t="str">
+        <v>Réalisé</v>
+      </c>
+      <c r="N51" t="str">
+        <v>Oui</v>
+      </c>
+      <c r="O51" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P51">
+        <v>-73917</v>
+      </c>
+      <c r="Q51">
+        <v>73917</v>
+      </c>
+      <c r="R51">
+        <v>9500</v>
+      </c>
+      <c r="S51" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-030, -2 ETP).</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>MV-051</v>
+      </c>
+      <c r="B52" t="str">
+        <v>M051</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Girard Ryan</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Attrition</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J52" t="str">
+        <v>AC-030</v>
+      </c>
+      <c r="K52" t="str">
+        <v>2026-08-15</v>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v>Planifié</v>
+      </c>
+      <c r="N52" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O52" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P52">
+        <v>-74650</v>
+      </c>
+      <c r="Q52">
+        <v>74650</v>
+      </c>
+      <c r="R52">
+        <v>3500</v>
+      </c>
+      <c r="S52" t="str">
+        <v>Mouvement de démo généré (attrition, lié à AC-030, -2 ETP).</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>MV-052</v>
+      </c>
+      <c r="B53" t="str">
+        <v>M052</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Bernard Sarah</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Départ forcé</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v>USA</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Claire Moreau</v>
+      </c>
+      <c r="J53" t="str">
+        <v>AC-030</v>
+      </c>
+      <c r="K53" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v>À faire</v>
+      </c>
+      <c r="N53" t="str">
+        <v>Non</v>
+      </c>
+      <c r="O53" t="str">
+        <v>Non</v>
+      </c>
+      <c r="P53">
+        <v>-75383</v>
+      </c>
+      <c r="Q53">
+        <v>75383</v>
+      </c>
+      <c r="R53">
+        <v>6500</v>
+      </c>
+      <c r="S53" t="str">
+        <v>Mouvement de démo généré (départ forcé, lié à AC-030, -2 ETP).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S53"/>
   </ignoredErrors>
 </worksheet>
 </file>